--- a/app/team_stats_2025_detailed.xlsx
+++ b/app/team_stats_2025_detailed.xlsx
@@ -726,82 +726,82 @@
         <v>30</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R2" s="1" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="S2" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T2" s="1" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="U2" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V2" s="1" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="W2" s="1" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="X2" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Z2" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA2" s="1" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AC2" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD2" s="1" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE2" s="1" t="n">
-        <v>67.56999999999999</v>
+        <v>68.42</v>
       </c>
       <c r="AF2" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AG2" s="1" t="n">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
       <c r="AH2" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AI2" s="1" t="n">
-        <v>13.51</v>
+        <v>13.16</v>
       </c>
       <c r="AJ2" s="1" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AK2" s="1" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL2" s="1" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AM2" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN2" s="1" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AO2" s="1" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -855,82 +855,82 @@
         <v>1</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q3" s="1" t="n">
         <v>7</v>
       </c>
       <c r="R3" s="1" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="S3" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="U3" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V3" s="1" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="X3" s="1" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Y3" s="1" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA3" s="1" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AB3" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC3" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD3" s="1" t="n">
         <v>14</v>
       </c>
       <c r="AE3" s="1" t="n">
-        <v>37.84</v>
+        <v>36.84</v>
       </c>
       <c r="AF3" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AG3" s="1" t="n">
-        <v>27.03</v>
+        <v>26.32</v>
       </c>
       <c r="AH3" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI3" s="1" t="n">
-        <v>35.14</v>
+        <v>36.84</v>
       </c>
       <c r="AJ3" s="1" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AK3" s="1" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AL3" s="1" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AM3" s="1" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AN3" s="1" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AO3" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -945,40 +945,40 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="O4" s="1" t="n">
         <v>14</v>
@@ -1023,40 +1023,40 @@
         <v>-4</v>
       </c>
       <c r="AC4" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD4" s="1" t="n">
         <v>17</v>
       </c>
       <c r="AE4" s="1" t="n">
-        <v>45.95</v>
+        <v>44.74</v>
       </c>
       <c r="AF4" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG4" s="1" t="n">
-        <v>21.62</v>
+        <v>23.68</v>
       </c>
       <c r="AH4" s="1" t="n">
         <v>12</v>
       </c>
       <c r="AI4" s="1" t="n">
-        <v>32.43</v>
+        <v>31.58</v>
       </c>
       <c r="AJ4" s="1" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AK4" s="1" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AL4" s="1" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AM4" s="1" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AN4" s="1" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AO4" s="1" t="n">
         <v>10</v>
@@ -1074,43 +1074,43 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>14</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>5.56</v>
+        <v>10.53</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>19</v>
@@ -1152,43 +1152,43 @@
         <v>11</v>
       </c>
       <c r="AC5" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD5" s="1" t="n">
         <v>23</v>
       </c>
       <c r="AE5" s="1" t="n">
-        <v>62.16</v>
+        <v>60.53</v>
       </c>
       <c r="AF5" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AG5" s="1" t="n">
-        <v>24.32</v>
+        <v>23.68</v>
       </c>
       <c r="AH5" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI5" s="1" t="n">
-        <v>13.51</v>
+        <v>15.79</v>
       </c>
       <c r="AJ5" s="1" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AK5" s="1" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AL5" s="1" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AM5" s="1" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AN5" s="1" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="AO5" s="1" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -1242,82 +1242,82 @@
         <v>15</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R6" s="1" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="S6" s="1" t="n">
         <v>8</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="U6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="V6" s="1" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Y6" s="1" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Z6" s="1" t="n">
         <v>26</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC6" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD6" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE6" s="1" t="n">
-        <v>51.35</v>
+        <v>52.63</v>
       </c>
       <c r="AF6" s="1" t="n">
         <v>11</v>
       </c>
       <c r="AG6" s="1" t="n">
-        <v>29.73</v>
+        <v>28.95</v>
       </c>
       <c r="AH6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AI6" s="1" t="n">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
       <c r="AJ6" s="1" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AK6" s="1" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AL6" s="1" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AM6" s="1" t="n">
         <v>50</v>
       </c>
       <c r="AN6" s="1" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AO6" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -1461,82 +1461,82 @@
         <v>22</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="R9" s="1" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="S9" s="1" t="n">
         <v>5</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="U9" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V9" s="1" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="W9" s="1" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="X9" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y9" s="1" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AA9" s="1" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AB9" s="1" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AC9" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD9" s="1" t="n">
         <v>21</v>
       </c>
       <c r="AE9" s="1" t="n">
-        <v>56.76</v>
+        <v>55.26</v>
       </c>
       <c r="AF9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AG9" s="1" t="n">
-        <v>16.22</v>
+        <v>15.79</v>
       </c>
       <c r="AH9" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI9" s="1" t="n">
-        <v>27.03</v>
+        <v>28.95</v>
       </c>
       <c r="AJ9" s="1" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AK9" s="1" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AL9" s="1" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AM9" s="1" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AN9" s="1" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AO9" s="1" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -1590,82 +1590,82 @@
         <v>47</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>12</v>
       </c>
       <c r="R10" s="1" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="S10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="U10" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10" s="1" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="W10" s="1" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="X10" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y10" s="1" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Z10" s="1" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA10" s="1" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC10" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD10" s="1" t="n">
         <v>31</v>
       </c>
       <c r="AE10" s="1" t="n">
-        <v>83.78</v>
+        <v>81.58</v>
       </c>
       <c r="AF10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AG10" s="1" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI10" s="1" t="n">
-        <v>13.51</v>
+        <v>15.79</v>
       </c>
       <c r="AJ10" s="1" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="AK10" s="1" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AL10" s="1" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AM10" s="1" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AN10" s="1" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AO10" s="1" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -1680,43 +1680,43 @@
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="M11" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N11" s="1" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="O11" s="1" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P11" s="1" t="n">
         <v>19</v>
@@ -1758,43 +1758,43 @@
         <v>13</v>
       </c>
       <c r="AC11" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD11" s="1" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE11" s="1" t="n">
-        <v>70.27</v>
+        <v>71.05</v>
       </c>
       <c r="AF11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AG11" s="1" t="n">
-        <v>13.51</v>
+        <v>13.16</v>
       </c>
       <c r="AH11" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AI11" s="1" t="n">
-        <v>16.22</v>
+        <v>15.79</v>
       </c>
       <c r="AJ11" s="1" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AK11" s="1" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AL11" s="1" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AM11" s="1" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AN11" s="1" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="AO11" s="1" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -2892,43 +2892,43 @@
         </is>
       </c>
       <c r="C23" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>9</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>5</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="H23" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O23" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="K23" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="L23" s="1" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M23" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="N23" s="1" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="O23" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="P23" s="1" t="n">
         <v>19</v>
@@ -2970,43 +2970,43 @@
         <v>14</v>
       </c>
       <c r="AC23" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD23" s="1" t="n">
         <v>20</v>
       </c>
       <c r="AE23" s="1" t="n">
-        <v>54.05</v>
+        <v>52.63</v>
       </c>
       <c r="AF23" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AG23" s="1" t="n">
-        <v>27.03</v>
+        <v>26.32</v>
       </c>
       <c r="AH23" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI23" s="1" t="n">
-        <v>18.92</v>
+        <v>21.05</v>
       </c>
       <c r="AJ23" s="1" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AK23" s="1" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AL23" s="1" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AM23" s="1" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AN23" s="1" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="AO23" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -3060,79 +3060,79 @@
         <v>34</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q24" s="1" t="n">
         <v>13</v>
       </c>
       <c r="R24" s="1" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="S24" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" s="1" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="U24" s="1" t="n">
         <v>3</v>
       </c>
       <c r="V24" s="1" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="W24" s="1" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="X24" s="1" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Y24" s="1" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z24" s="1" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AA24" s="1" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AB24" s="1" t="n">
         <v>20</v>
       </c>
       <c r="AC24" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD24" s="1" t="n">
         <v>27</v>
       </c>
       <c r="AE24" s="1" t="n">
-        <v>72.97</v>
+        <v>71.05</v>
       </c>
       <c r="AF24" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG24" s="1" t="n">
-        <v>13.51</v>
+        <v>15.79</v>
       </c>
       <c r="AH24" s="1" t="n">
         <v>5</v>
       </c>
       <c r="AI24" s="1" t="n">
-        <v>13.51</v>
+        <v>13.16</v>
       </c>
       <c r="AJ24" s="1" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AK24" s="1" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AL24" s="1" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AM24" s="1" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AN24" s="1" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="AO24" s="1" t="n">
         <v>54</v>
@@ -3189,79 +3189,79 @@
         <v>19</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="R25" s="1" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="S25" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" s="1" t="n">
-        <v>22.22</v>
+        <v>26.32</v>
       </c>
       <c r="U25" s="1" t="n">
         <v>5</v>
       </c>
       <c r="V25" s="1" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="W25" s="1" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="X25" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y25" s="1" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z25" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA25" s="1" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AB25" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AC25" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD25" s="1" t="n">
         <v>19</v>
       </c>
       <c r="AE25" s="1" t="n">
-        <v>51.35</v>
+        <v>50</v>
       </c>
       <c r="AF25" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG25" s="1" t="n">
-        <v>29.73</v>
+        <v>31.58</v>
       </c>
       <c r="AH25" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AI25" s="1" t="n">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
       <c r="AJ25" s="1" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AK25" s="1" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AL25" s="1" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AM25" s="1" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AN25" s="1" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="AO25" s="1" t="n">
         <v>27</v>
@@ -3279,43 +3279,43 @@
         </is>
       </c>
       <c r="C26" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>6</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="H26" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="K26" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="L26" s="1" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M26" s="1" t="n">
-        <v>24</v>
-      </c>
       <c r="N26" s="1" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="O26" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>19</v>
@@ -3357,43 +3357,43 @@
         <v>-1</v>
       </c>
       <c r="AC26" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD26" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE26" s="1" t="n">
-        <v>35.14</v>
+        <v>36.84</v>
       </c>
       <c r="AF26" s="1" t="n">
         <v>12</v>
       </c>
       <c r="AG26" s="1" t="n">
-        <v>32.43</v>
+        <v>31.58</v>
       </c>
       <c r="AH26" s="1" t="n">
         <v>12</v>
       </c>
       <c r="AI26" s="1" t="n">
-        <v>32.43</v>
+        <v>31.58</v>
       </c>
       <c r="AJ26" s="1" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AK26" s="1" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AL26" s="1" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AM26" s="1" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AN26" s="1" t="n">
         <v>1.05</v>
       </c>
       <c r="AO26" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3408,43 +3408,43 @@
         </is>
       </c>
       <c r="C27" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>4</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="H27" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="K27" s="1" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L27" s="1" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="M27" s="1" t="n">
         <v>18</v>
       </c>
       <c r="N27" s="1" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="O27" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P27" s="1" t="n">
         <v>19</v>
@@ -3486,43 +3486,43 @@
         <v>7</v>
       </c>
       <c r="AC27" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD27" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE27" s="1" t="n">
-        <v>59.46</v>
+        <v>60.53</v>
       </c>
       <c r="AF27" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AG27" s="1" t="n">
-        <v>18.92</v>
+        <v>18.42</v>
       </c>
       <c r="AH27" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AI27" s="1" t="n">
-        <v>21.62</v>
+        <v>21.05</v>
       </c>
       <c r="AJ27" s="1" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AK27" s="1" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AL27" s="1" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AM27" s="1" t="n">
         <v>36</v>
       </c>
       <c r="AN27" s="1" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AO27" s="1" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -3576,82 +3576,82 @@
         <v>23</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R28" s="1" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="S28" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T28" s="1" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="U28" s="1" t="n">
         <v>8</v>
       </c>
       <c r="V28" s="1" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="W28" s="1" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="X28" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y28" s="1" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z28" s="1" t="n">
         <v>21</v>
       </c>
       <c r="AA28" s="1" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AB28" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC28" s="1" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AD28" s="1" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE28" s="1" t="n">
-        <v>59.46</v>
+        <v>60.53</v>
       </c>
       <c r="AF28" s="1" t="n">
         <v>4</v>
       </c>
       <c r="AG28" s="1" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="AH28" s="1" t="n">
         <v>11</v>
       </c>
       <c r="AI28" s="1" t="n">
-        <v>29.73</v>
+        <v>28.95</v>
       </c>
       <c r="AJ28" s="1" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AK28" s="1" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AL28" s="1" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AM28" s="1" t="n">
         <v>31</v>
       </c>
       <c r="AN28" s="1" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="AO28" s="1" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
